--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -50474,6 +50474,166 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P673" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S673" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T673" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U673" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V673" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W673" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X673" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB673" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC673" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD673" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL673" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM673" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO673" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP673" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ673" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR673" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS673" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT673" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU673" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV673" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P674" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S674" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T674" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U674" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V674" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W674" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X674" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB674" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC674" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD674" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL674" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM674" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO674" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP674" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ674" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR674" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS674" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT674" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU674" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV674" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -50634,6 +50634,326 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P675" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S675" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T675" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U675" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V675" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W675" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X675" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB675" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC675" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD675" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL675" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM675" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO675" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP675" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ675" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR675" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS675" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT675" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU675" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV675" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P676" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S676" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T676" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U676" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V676" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W676" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X676" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB676" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC676" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD676" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL676" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM676" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO676" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP676" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ676" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR676" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS676" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT676" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU676" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV676" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P677" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S677" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T677" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U677" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V677" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W677" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X677" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB677" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC677" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD677" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL677" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM677" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO677" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP677" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ677" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR677" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS677" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT677" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU677" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV677" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P678" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S678" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T678" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U678" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V678" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W678" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X678" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB678" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC678" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD678" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL678" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM678" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO678" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP678" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ678" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR678" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS678" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT678" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU678" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV678" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -50954,6 +50954,486 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P679" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S679" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T679" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U679" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V679" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W679" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X679" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB679" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC679" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD679" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL679" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM679" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO679" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP679" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ679" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR679" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS679" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT679" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU679" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV679" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P680" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S680" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T680" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U680" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V680" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W680" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X680" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB680" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC680" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD680" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL680" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM680" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO680" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP680" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ680" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR680" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS680" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT680" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU680" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV680" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P681" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S681" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T681" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U681" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V681" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W681" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X681" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB681" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC681" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD681" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL681" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM681" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO681" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP681" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ681" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR681" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS681" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT681" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU681" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV681" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P682" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S682" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T682" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U682" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V682" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W682" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X682" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB682" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC682" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD682" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL682" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM682" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO682" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP682" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ682" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR682" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS682" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT682" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU682" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV682" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P683" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S683" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T683" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U683" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V683" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W683" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X683" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB683" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC683" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD683" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL683" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM683" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO683" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP683" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ683" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR683" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS683" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT683" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU683" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV683" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P684" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S684" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T684" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U684" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V684" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W684" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X684" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB684" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC684" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD684" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL684" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM684" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO684" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP684" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ684" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR684" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS684" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT684" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU684" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV684" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -51434,6 +51434,166 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P685" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S685" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T685" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U685" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V685" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W685" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X685" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB685" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC685" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD685" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL685" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM685" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO685" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP685" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ685" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR685" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS685" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT685" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU685" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV685" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P686" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S686" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T686" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U686" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V686" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W686" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X686" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB686" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC686" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD686" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL686" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM686" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO686" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP686" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ686" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR686" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS686" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT686" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU686" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV686" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -51594,6 +51594,246 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P687" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S687" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T687" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U687" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V687" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W687" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X687" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB687" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC687" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD687" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL687" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM687" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO687" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP687" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ687" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR687" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS687" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT687" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU687" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV687" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P688" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S688" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T688" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U688" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V688" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W688" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X688" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB688" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC688" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD688" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL688" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM688" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO688" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP688" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ688" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR688" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS688" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT688" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU688" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV688" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P689" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S689" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T689" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U689" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V689" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W689" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X689" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB689" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC689" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD689" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL689" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM689" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO689" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP689" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ689" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR689" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS689" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT689" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU689" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV689" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -51834,6 +51834,806 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P690" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S690" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T690" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U690" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V690" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W690" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X690" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB690" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC690" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD690" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL690" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM690" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO690" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP690" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ690" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR690" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS690" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT690" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU690" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV690" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P691" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S691" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T691" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U691" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V691" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W691" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X691" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB691" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC691" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD691" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL691" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM691" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO691" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP691" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ691" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR691" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS691" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT691" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU691" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV691" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P692" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S692" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T692" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U692" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V692" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W692" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X692" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB692" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC692" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD692" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL692" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM692" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO692" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP692" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ692" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR692" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS692" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT692" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU692" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV692" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P693" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S693" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T693" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U693" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V693" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W693" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X693" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB693" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC693" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD693" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL693" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM693" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO693" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP693" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ693" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR693" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS693" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT693" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU693" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV693" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P694" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S694" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T694" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U694" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V694" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W694" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X694" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB694" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC694" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD694" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL694" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM694" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO694" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP694" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ694" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR694" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS694" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT694" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU694" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV694" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P695" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S695" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T695" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U695" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V695" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W695" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X695" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB695" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC695" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD695" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL695" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM695" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO695" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP695" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ695" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR695" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS695" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT695" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU695" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV695" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P696" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S696" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T696" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U696" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V696" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W696" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X696" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB696" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC696" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD696" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL696" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM696" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO696" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP696" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ696" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR696" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS696" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT696" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU696" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV696" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P697" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S697" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T697" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U697" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V697" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W697" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X697" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB697" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC697" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD697" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL697" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM697" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO697" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP697" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ697" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR697" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS697" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT697" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU697" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV697" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P698" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S698" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T698" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U698" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V698" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W698" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X698" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB698" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC698" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD698" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL698" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM698" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO698" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP698" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ698" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR698" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS698" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT698" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU698" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV698" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P699" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S699" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T699" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U699" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V699" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W699" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X699" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB699" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC699" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD699" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL699" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM699" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO699" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP699" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ699" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR699" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS699" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT699" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU699" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV699" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -52634,6 +52634,86 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P700" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S700" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T700" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U700" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V700" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W700" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X700" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB700" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC700" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD700" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL700" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM700" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO700" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP700" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ700" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR700" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS700" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT700" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU700" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV700" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -52714,6 +52714,166 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P701" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S701" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T701" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U701" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V701" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W701" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X701" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB701" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC701" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD701" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL701" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM701" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO701" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP701" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ701" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR701" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS701" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT701" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU701" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV701" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P702" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S702" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T702" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U702" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V702" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W702" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X702" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB702" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC702" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD702" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL702" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM702" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO702" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP702" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ702" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR702" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS702" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT702" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU702" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV702" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
